--- a/BlazeDemo/src/test/resources/testdata/BookingResult.xlsx
+++ b/BlazeDemo/src/test/resources/testdata/BookingResult.xlsx
@@ -29,7 +29,7 @@
     <t>BookingDate</t>
   </si>
   <si>
-    <t>1780723231540</t>
+    <t>1780730903438</t>
   </si>
   <si>
     <t>PendingCapture</t>
@@ -41,7 +41,7 @@
     <t>xxxxxxxxxxxx1111</t>
   </si>
   <si>
-    <t>Sat, 06 Jun 2026 05:20:31 +0000</t>
+    <t>Sat, 06 Jun 2026 07:28:23 +0000</t>
   </si>
 </sst>
 </file>

--- a/BlazeDemo/src/test/resources/testdata/BookingResult.xlsx
+++ b/BlazeDemo/src/test/resources/testdata/BookingResult.xlsx
@@ -29,7 +29,7 @@
     <t>BookingDate</t>
   </si>
   <si>
-    <t>1780730903438</t>
+    <t>1780730994535</t>
   </si>
   <si>
     <t>PendingCapture</t>
@@ -41,7 +41,7 @@
     <t>xxxxxxxxxxxx1111</t>
   </si>
   <si>
-    <t>Sat, 06 Jun 2026 07:28:23 +0000</t>
+    <t>Sat, 06 Jun 2026 07:29:54 +0000</t>
   </si>
 </sst>
 </file>
